--- a/registration_forms/027_security_program_registration_form--registration_forms.xlsx
+++ b/registration_forms/027_security_program_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>participant_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>registration_form</t>
+          <t>Participant Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>Event Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,63 +561,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_info</t>
+          <t>participant_contact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>participant_info</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_info_1</t>
+          <t>participant_experience</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>participant</t>
+          <t>Security Experience</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_info_2</t>
+          <t>participant_skills</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>participant</t>
+          <t>Skills or Certifications</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,35 +635,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>participant_info_3</t>
+          <t>update_preferences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant</t>
+          <t>Update Preferences</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_info_4</t>
+          <t>background_check</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>participant</t>
+          <t>Background Check</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,16 +681,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>registration_form_1</t>
+          <t>mailing_list</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>participant</t>
+          <t>Mailing List</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>first_time_attending</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>First Time Attending</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>participant_phone</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>participant_notes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -769,32 +861,134 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>participant_info_choices</t>
+          <t>participant_skills_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>penetration_testing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>participant_info_choices</t>
+          <t>participant_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>vulnerability_assessment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Vulnerability Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>participant_skills_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cybersecurity_consulting</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cybersecurity Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>participant_skills_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>security_research</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Security Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>background_check_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>background_check_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>first_time_attending_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>first_time_attending_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
